--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_02/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_02/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>36.1047448323258</v>
+        <v>37.771035565999</v>
       </c>
       <c r="B2" t="n">
-        <v>58.09383677841461</v>
+        <v>55.16251361059032</v>
       </c>
       <c r="C2" t="n">
-        <v>46.36003343303624</v>
+        <v>38.58524416734394</v>
       </c>
       <c r="D2" t="n">
-        <v>5.47424186258545</v>
+        <v>6.4441115629895</v>
       </c>
       <c r="E2" t="n">
-        <v>3.00578806869876</v>
+        <v>4.202465328304597</v>
       </c>
       <c r="F2" t="n">
-        <v>2.278249194072044</v>
+        <v>2.463973760303255</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1646747083330305</v>
+        <v>0.136420249671501</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.007714548371249639</v>
+        <v>-0.005951444277281215</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4447732454084209</v>
+        <v>-0.4437655910088536</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.6011193442832695</v>
+        <v>-0.6009717469901446</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0005037129726038952</v>
+        <v>-2.369586660974905e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6438176938330392</v>
+        <v>-0.5269296129260391</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0009467354108912131</v>
+        <v>-0.003223639046920773</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99.99999999017216</v>
+        <v>99.99998860729569</v>
       </c>
       <c r="B3" t="n">
-        <v>110.1971328566008</v>
+        <v>93.3558413193916</v>
       </c>
       <c r="C3" t="n">
-        <v>46.3447070854503</v>
+        <v>38.85929417852031</v>
       </c>
       <c r="D3" t="n">
-        <v>7.229297277235525</v>
+        <v>8.732501363370019</v>
       </c>
       <c r="E3" t="n">
-        <v>2.542570098854799</v>
+        <v>4.344112958940269</v>
       </c>
       <c r="F3" t="n">
-        <v>7.920385403699688</v>
+        <v>8.137499204061102</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004438719522941011</v>
+        <v>0.004382162276210646</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9491089897042649</v>
+        <v>-0.9419355475627865</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9679926365321201</v>
+        <v>-0.963209831910088</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9919200502618427</v>
+        <v>-0.9904147552455446</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.00215028007200987</v>
+        <v>-0.0001232003187072189</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6220069729206215</v>
+        <v>-0.5874999188269817</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0003954324728524518</v>
+        <v>-0.0671686416547386</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99.99999999017216</v>
+        <v>46.69792883371544</v>
       </c>
       <c r="B4" t="n">
-        <v>57.07682442122123</v>
+        <v>53.8738429912204</v>
       </c>
       <c r="C4" t="n">
-        <v>46.3447070854503</v>
+        <v>38.58564042386213</v>
       </c>
       <c r="D4" t="n">
-        <v>7.229297277235525</v>
+        <v>5.77206221360351</v>
       </c>
       <c r="E4" t="n">
-        <v>4.61324938821601</v>
+        <v>4.404120663198319</v>
       </c>
       <c r="F4" t="n">
-        <v>7.920385403699688</v>
+        <v>3.270636565411594</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004438719522941011</v>
+        <v>0.0606982408735688</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9491089897042649</v>
+        <v>-0.4700938532255397</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9679926365321201</v>
+        <v>-0.6726384127890429</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9919200502618427</v>
+        <v>-0.8264988618718361</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.00215028007200987</v>
+        <v>-0.2594892174339121</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6220069729206215</v>
+        <v>-0.7069656135249494</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0003954324728524518</v>
+        <v>-0.003316098901164771</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>49.86769426279845</v>
+        <v>52.28692143632548</v>
       </c>
       <c r="B5" t="n">
-        <v>64.54475946365332</v>
+        <v>64.27182353865744</v>
       </c>
       <c r="C5" t="n">
-        <v>46.35918162324759</v>
+        <v>38.58556518579302</v>
       </c>
       <c r="D5" t="n">
-        <v>5.000907494176905</v>
+        <v>8.505514508281841</v>
       </c>
       <c r="E5" t="n">
-        <v>2.95979508519803</v>
+        <v>4.01964376599155</v>
       </c>
       <c r="F5" t="n">
-        <v>3.410856131766367</v>
+        <v>3.61045969184599</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04849659249004988</v>
+        <v>0.04111882599062225</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6192670946684641</v>
+        <v>-0.6202293207914124</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.756400319162755</v>
+        <v>-0.756672465956766</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.887819244321326</v>
+        <v>-0.8881971549005961</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1719806582475035</v>
+        <v>-0.001379695540458602</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.669263023180985</v>
+        <v>-0.5985794762421699</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0009160950227299949</v>
+        <v>-0.003298543351703265</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66.96823338725684</v>
+        <v>83.67994694298237</v>
       </c>
       <c r="B6" t="n">
-        <v>59.5815467462388</v>
+        <v>100.3228680269387</v>
       </c>
       <c r="C6" t="n">
-        <v>46.38138036152014</v>
+        <v>38.64288550983116</v>
       </c>
       <c r="D6" t="n">
-        <v>5.300922351245262</v>
+        <v>11.90932595365925</v>
       </c>
       <c r="E6" t="n">
-        <v>2.986002700492977</v>
+        <v>4.670490907970355</v>
       </c>
       <c r="F6" t="n">
-        <v>4.858902692669032</v>
+        <v>6.399321663641322</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01678303844660896</v>
+        <v>0.008072094714520221</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8395935773541469</v>
+        <v>-0.9027969832961565</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8963887925460298</v>
+        <v>-0.9387915213481045</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9640222848631461</v>
+        <v>-0.9811863800742622</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.02648328945514964</v>
+        <v>-0.1232566759681957</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6946732205277589</v>
+        <v>-0.4712196219687493</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.001714604227991373</v>
+        <v>-0.01667328562727027</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>41.74994474537162</v>
+        <v>56.77010982836906</v>
       </c>
       <c r="B7" t="n">
-        <v>59.88147108902741</v>
+        <v>66.56704277128371</v>
       </c>
       <c r="C7" t="n">
-        <v>46.46433392765639</v>
+        <v>39.46866740954379</v>
       </c>
       <c r="D7" t="n">
-        <v>5.398461057450803</v>
+        <v>8.251920428417257</v>
       </c>
       <c r="E7" t="n">
-        <v>2.339550540769143</v>
+        <v>3.365293154944879</v>
       </c>
       <c r="F7" t="n">
-        <v>2.714981340100781</v>
+        <v>4.063390955413303</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09461466065919773</v>
+        <v>0.03030870661765602</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3555780587789311</v>
+        <v>-0.7010225890847187</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.61269409108837</v>
+        <v>-0.8049196367200613</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7749162315326306</v>
+        <v>-0.9182505061219266</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.094535185936254</v>
+        <v>-0.02717951006618723</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6973958320575693</v>
+        <v>-0.6095440289130041</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.004698520942347711</v>
+        <v>-0.2093557288935513</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>40.46068202952475</v>
+        <v>40.46340779323927</v>
       </c>
       <c r="B8" t="n">
-        <v>58.61604026447151</v>
+        <v>52.33379788796353</v>
       </c>
       <c r="C8" t="n">
-        <v>46.34501822565772</v>
+        <v>38.59103737181176</v>
       </c>
       <c r="D8" t="n">
-        <v>5.404818078495397</v>
+        <v>6.143091650900868</v>
       </c>
       <c r="E8" t="n">
-        <v>2.086423882144203</v>
+        <v>4.76829715526466</v>
       </c>
       <c r="F8" t="n">
-        <v>2.590087184951505</v>
+        <v>2.675648820669727</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1066293640651617</v>
+        <v>0.1046410035234236</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2926463264737243</v>
+        <v>-0.1902737985202077</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5808170495971917</v>
+        <v>-0.530405814673053</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7453295869786782</v>
+        <v>-0.6960765244282168</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0008189935556365842</v>
+        <v>-0.08220481753578761</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6893700967345791</v>
+        <v>-0.4219270960636686</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0004066244747000958</v>
+        <v>-0.004575386756076744</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>37.37004914154102</v>
+        <v>38.45415762580542</v>
       </c>
       <c r="B9" t="n">
-        <v>62.88432989100357</v>
+        <v>54.46117865422296</v>
       </c>
       <c r="C9" t="n">
-        <v>46.35613559491931</v>
+        <v>38.60289747579163</v>
       </c>
       <c r="D9" t="n">
-        <v>6.021116115733276</v>
+        <v>6.328384386369446</v>
       </c>
       <c r="E9" t="n">
-        <v>2.233147529930404</v>
+        <v>3.360282120702429</v>
       </c>
       <c r="F9" t="n">
-        <v>2.385999460243445</v>
+        <v>2.51160461269846</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1450357666663115</v>
+        <v>0.1272769704050745</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1036534063836705</v>
+        <v>-0.05767153228088694</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4891401896636128</v>
+        <v>-0.4676095058426041</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6512242365065863</v>
+        <v>-0.6283078504687345</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.01418899289783424</v>
+        <v>-0.007205774917937104</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6701307274155075</v>
+        <v>-0.5002878525935889</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.000806526558533736</v>
+        <v>-0.007342744351380992</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>92.76801887561338</v>
+        <v>45.19439206092815</v>
       </c>
       <c r="B10" t="n">
-        <v>81.84539364675308</v>
+        <v>53.8522605084552</v>
       </c>
       <c r="C10" t="n">
-        <v>46.36408749706573</v>
+        <v>38.59879891000744</v>
       </c>
       <c r="D10" t="n">
-        <v>8.482741912149612</v>
+        <v>5.331294665807532</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9810122562902</v>
+        <v>4.862372606946733</v>
       </c>
       <c r="F10" t="n">
-        <v>7.099315897509168</v>
+        <v>3.05451453502763</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005709791791191408</v>
+        <v>0.06853658501933103</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.936926991532902</v>
+        <v>-0.4162430415367087</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9600020235119641</v>
+        <v>-0.6439913095691123</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9893152223267671</v>
+        <v>-0.8028195056836787</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0192999597711991</v>
+        <v>-0.004110257916006907</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5679835697092557</v>
+        <v>-0.705841702861761</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.001092563854225621</v>
+        <v>-0.00638641233506862</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>41.02841727182359</v>
+        <v>39.83308128035711</v>
       </c>
       <c r="B11" t="n">
-        <v>54.97637038676283</v>
+        <v>53.11823791602551</v>
       </c>
       <c r="C11" t="n">
-        <v>46.36029271558443</v>
+        <v>38.58483332307989</v>
       </c>
       <c r="D11" t="n">
-        <v>5.292346148665375</v>
+        <v>6.30342132747702</v>
       </c>
       <c r="E11" t="n">
-        <v>2.965349387291565</v>
+        <v>4.981499299365632</v>
       </c>
       <c r="F11" t="n">
-        <v>2.642475950887692</v>
+        <v>2.635388550482287</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1010135506478057</v>
+        <v>0.1111933679542786</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3214316302853763</v>
+        <v>-0.1514883347953898</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5953205927417453</v>
+        <v>-0.5117652553447788</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7590050248384326</v>
+        <v>-0.6765947935020736</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.04399257786034837</v>
+        <v>-0.08756438077993174</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6844105072018917</v>
+        <v>-0.4465098300660729</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0009560620446376936</v>
+        <v>-0.003127775385309006</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>63.3630158671219</v>
+        <v>45.11600159432211</v>
       </c>
       <c r="B12" t="n">
-        <v>81.76119502369266</v>
+        <v>57.34556642043868</v>
       </c>
       <c r="C12" t="n">
-        <v>46.36026021711553</v>
+        <v>38.58549311157331</v>
       </c>
       <c r="D12" t="n">
-        <v>6.036940768827256</v>
+        <v>5.348813004497449</v>
       </c>
       <c r="E12" t="n">
-        <v>2.464555895386158</v>
+        <v>4.911324465594306</v>
       </c>
       <c r="F12" t="n">
-        <v>4.511040703482897</v>
+        <v>3.048080028636238</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02051960607329526</v>
+        <v>0.06899114110438601</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8113085600547472</v>
+        <v>-0.413221837109288</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8767311719853179</v>
+        <v>-0.6424012623398579</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9554429858526132</v>
+        <v>-0.8014649515002471</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.02519052960271369</v>
+        <v>-0.00362607367104113</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6707343527348605</v>
+        <v>-0.7053762594662876</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0009548930445688784</v>
+        <v>-0.003281726033770999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96.87731725492328</v>
+        <v>54.1764350073862</v>
       </c>
       <c r="B13" t="n">
-        <v>92.83455451886735</v>
+        <v>71.55294033486962</v>
       </c>
       <c r="C13" t="n">
-        <v>46.36361640695892</v>
+        <v>38.59945214835093</v>
       </c>
       <c r="D13" t="n">
-        <v>7.796603599386021</v>
+        <v>8.731309971110067</v>
       </c>
       <c r="E13" t="n">
-        <v>2.562841713252187</v>
+        <v>4.76142789905072</v>
       </c>
       <c r="F13" t="n">
-        <v>7.560320294348034</v>
+        <v>3.827878399832263</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004933433297635921</v>
+        <v>0.03607867519237803</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.94428953810211</v>
+        <v>-0.6566543543456963</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9647971242379373</v>
+        <v>-0.777849224422407</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9909108257301168</v>
+        <v>-0.9018317784318272</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.01148402517517144</v>
+        <v>-0.02331389396774804</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5986803151438314</v>
+        <v>-0.5931174217134461</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.001075618306142126</v>
+        <v>-0.006538834615215788</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>36.54697446136812</v>
+        <v>88.33985348453672</v>
       </c>
       <c r="B14" t="n">
-        <v>58.0583528685553</v>
+        <v>71.55294033486962</v>
       </c>
       <c r="C14" t="n">
-        <v>46.36003343303624</v>
+        <v>38.59945214835093</v>
       </c>
       <c r="D14" t="n">
-        <v>5.47424186258545</v>
+        <v>10.64497820334155</v>
       </c>
       <c r="E14" t="n">
-        <v>2.584294157301906</v>
+        <v>4.76142789905072</v>
       </c>
       <c r="F14" t="n">
-        <v>2.317530022496092</v>
+        <v>6.81057738731624</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1571288972493639</v>
+        <v>0.006664278678723057</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.043038830063624</v>
+        <v>-0.9170095754444674</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4610143668935685</v>
+        <v>-0.9474237265574993</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6198549287265158</v>
+        <v>-0.9847156305102508</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.03147278158066825</v>
+        <v>-0.02190801885167286</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6418791742458932</v>
+        <v>-0.5044214560773241</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0009467354108912131</v>
+        <v>-0.006538834615215788</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>55.75325539974636</v>
+        <v>61.2509365087587</v>
       </c>
       <c r="B15" t="n">
-        <v>96.22435739157591</v>
+        <v>53.14505375727047</v>
       </c>
       <c r="C15" t="n">
-        <v>46.35896746550291</v>
+        <v>38.57826804210192</v>
       </c>
       <c r="D15" t="n">
-        <v>7.559818764003968</v>
+        <v>7.092958236817974</v>
       </c>
       <c r="E15" t="n">
-        <v>2.294443211513499</v>
+        <v>4.934827074135359</v>
       </c>
       <c r="F15" t="n">
-        <v>3.853404666891455</v>
+        <v>4.397819719738477</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03295628469040584</v>
+        <v>0.02282038417061876</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7248372764436547</v>
+        <v>-0.7620366392051161</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8199681100451104</v>
+        <v>-0.8440248218145576</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9266799593319598</v>
+        <v>-0.9397162672051119</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.07676322036200776</v>
+        <v>-0.05043015532551313</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.620205071562026</v>
+        <v>-0.2616807043316781</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0009083915700202014</v>
+        <v>-0.001595876490447651</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>54.52766026510893</v>
+        <v>99.99998068131633</v>
       </c>
       <c r="B16" t="n">
-        <v>87.44027664618811</v>
+        <v>64.31731915596592</v>
       </c>
       <c r="C16" t="n">
-        <v>46.36000305577164</v>
+        <v>38.85929417852031</v>
       </c>
       <c r="D16" t="n">
-        <v>7.49693975793013</v>
+        <v>8.732501363370019</v>
       </c>
       <c r="E16" t="n">
-        <v>3.462747417515583</v>
+        <v>4.906780567343795</v>
       </c>
       <c r="F16" t="n">
-        <v>3.719112958583131</v>
+        <v>8.137498083552339</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03576641241493994</v>
+        <v>0.00438216340467904</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7062171102751513</v>
+        <v>-0.9419355344576191</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8083172990113511</v>
+        <v>-0.9632098233961351</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.920064217325005</v>
+        <v>-0.9904147524348227</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01192233738183349</v>
+        <v>-0.000122899259146093</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6120670439029886</v>
+        <v>-0.5874998623543788</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0009456427125082397</v>
+        <v>-0.0671686416547386</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>36.85610300902099</v>
+        <v>51.03208658896595</v>
       </c>
       <c r="B17" t="n">
-        <v>58.0831963790327</v>
+        <v>66.65357717387793</v>
       </c>
       <c r="C17" t="n">
-        <v>46.35965998117603</v>
+        <v>39.46671727232963</v>
       </c>
       <c r="D17" t="n">
-        <v>5.791367980084758</v>
+        <v>8.643098997898658</v>
       </c>
       <c r="E17" t="n">
-        <v>2.990331126369089</v>
+        <v>3.365293154944879</v>
       </c>
       <c r="F17" t="n">
-        <v>2.363962960160018</v>
+        <v>3.528981734680387</v>
       </c>
       <c r="G17" t="n">
-        <v>0.152466811544752</v>
+        <v>0.04510548270903019</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.06640562104985187</v>
+        <v>-0.5918443370711693</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.471792723319157</v>
+        <v>-0.740178735717742</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6320177210734713</v>
+        <v>-0.8769950212894823</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.07817965081977879</v>
+        <v>-0.009516334567767811</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.648981136418785</v>
+        <v>-0.5902139105931064</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0009333020010987412</v>
+        <v>-0.2089006968769146</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>39.61156883362769</v>
+        <v>95.68174965651095</v>
       </c>
       <c r="B18" t="n">
-        <v>58.32070193476157</v>
+        <v>53.67567746928414</v>
       </c>
       <c r="C18" t="n">
-        <v>46.36000573857423</v>
+        <v>38.60022676239963</v>
       </c>
       <c r="D18" t="n">
-        <v>5.810740893816441</v>
+        <v>9.716702876009663</v>
       </c>
       <c r="E18" t="n">
-        <v>3.472428341874022</v>
+        <v>4.982474454375184</v>
       </c>
       <c r="F18" t="n">
-        <v>2.561552025967397</v>
+        <v>7.652747043710656</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1158614337673981</v>
+        <v>0.005081586594754483</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2463877072367383</v>
+        <v>-0.9340813900293331</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.557812814690321</v>
+        <v>-0.9581110381726762</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7229467588714791</v>
+        <v>-0.9886886453713493</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.08237093291475775</v>
+        <v>-0.05336824632313483</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6840843177496093</v>
+        <v>-0.5567324663026404</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0009457392154059441</v>
+        <v>-0.006719577893247453</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>86.46922813688293</v>
+        <v>41.08863991152743</v>
       </c>
       <c r="B19" t="n">
-        <v>78.50314188017836</v>
+        <v>52.34733445570708</v>
       </c>
       <c r="C19" t="n">
-        <v>46.34644927964951</v>
+        <v>38.58701769278757</v>
       </c>
       <c r="D19" t="n">
-        <v>9.467933350530283</v>
+        <v>6.037003240688182</v>
       </c>
       <c r="E19" t="n">
-        <v>2.296653450666638</v>
+        <v>4.888632441332626</v>
       </c>
       <c r="F19" t="n">
-        <v>6.429896642751776</v>
+        <v>2.722746038282441</v>
       </c>
       <c r="G19" t="n">
-        <v>0.007269433668842553</v>
+        <v>0.09864687185723295</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9227665039290032</v>
+        <v>-0.2264105332136234</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9510447723172318</v>
+        <v>-0.5479829868455423</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9860789190423628</v>
+        <v>-0.7139454444611274</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.03306375530551185</v>
+        <v>-0.02142057485038931</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5209311636766364</v>
+        <v>-0.4386316833619577</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0004581008141047828</v>
+        <v>-0.003637461650432688</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>94.35535633169823</v>
+        <v>39.45663339820096</v>
       </c>
       <c r="B20" t="n">
-        <v>52.7440632412022</v>
+        <v>53.68151465607402</v>
       </c>
       <c r="C20" t="n">
-        <v>46.34505453753148</v>
+        <v>38.59902935521417</v>
       </c>
       <c r="D20" t="n">
-        <v>8.091403019527331</v>
+        <v>6.14260254222434</v>
       </c>
       <c r="E20" t="n">
-        <v>2.959832348495012</v>
+        <v>4.808252646422604</v>
       </c>
       <c r="F20" t="n">
-        <v>7.321809599840099</v>
+        <v>2.580952588320522</v>
       </c>
       <c r="G20" t="n">
-        <v>0.005381049218458066</v>
+        <v>0.1152219106961761</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9399455949294476</v>
+        <v>-0.1272442581404597</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9619770021612977</v>
+        <v>-0.5002477311904784</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9899798574567032</v>
+        <v>-0.664301450889342</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.02728672517576194</v>
+        <v>-0.01408464622143756</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5617351512858055</v>
+        <v>-0.4611912974701625</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0004079306464788999</v>
+        <v>-0.006440182883306333</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>47.50222721545104</v>
+        <v>70.10751104224765</v>
       </c>
       <c r="B21" t="n">
-        <v>67.24530711434923</v>
+        <v>54.16056740610847</v>
       </c>
       <c r="C21" t="n">
-        <v>46.36022797876919</v>
+        <v>38.57559843403553</v>
       </c>
       <c r="D21" t="n">
-        <v>5.000305666062514</v>
+        <v>6.281659108903431</v>
       </c>
       <c r="E21" t="n">
-        <v>2.541434848236653</v>
+        <v>4.82787955404305</v>
       </c>
       <c r="F21" t="n">
-        <v>3.172031559227185</v>
+        <v>5.395641934091238</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0581352906702693</v>
+        <v>0.0140380533257926</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5604419415042095</v>
+        <v>-0.8394010897150674</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7226373087917576</v>
+        <v>-0.8961547080258959</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8643577863050088</v>
+        <v>-0.9639919336578862</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.04754726645873771</v>
+        <v>-0.1593521976024251</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7016717560199955</v>
+        <v>-0.6940142366009019</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0009537334013494093</v>
+        <v>-0.000972967941622882</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>65.01449920166189</v>
+        <v>67.50825221348687</v>
       </c>
       <c r="B22" t="n">
-        <v>74.30231413562478</v>
+        <v>84.69215203467138</v>
       </c>
       <c r="C22" t="n">
-        <v>46.34533302344826</v>
+        <v>38.64915484943576</v>
       </c>
       <c r="D22" t="n">
-        <v>5.842762707426203</v>
+        <v>6.410699698384133</v>
       </c>
       <c r="E22" t="n">
-        <v>3.692949034909179</v>
+        <v>4.459123586412485</v>
       </c>
       <c r="F22" t="n">
-        <v>4.684876173963579</v>
+        <v>5.075684083643302</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0186936013594386</v>
+        <v>0.01605283297810337</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8250252943558248</v>
+        <v>-0.8206239301309294</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8861791834028684</v>
+        <v>-0.883046569442152</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9596571801400555</v>
+        <v>-0.9583571108882812</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.06845445641781943</v>
+        <v>-0.03081710870895846</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6817003044387256</v>
+        <v>-0.6775522640187501</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0004179480432043831</v>
+        <v>-0.01813613153501065</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>52.94495142477955</v>
+        <v>90.23375533865573</v>
       </c>
       <c r="B23" t="n">
-        <v>90.68324989181103</v>
+        <v>53.90708302885389</v>
       </c>
       <c r="C23" t="n">
-        <v>46.36669630642356</v>
+        <v>38.60340368908366</v>
       </c>
       <c r="D23" t="n">
-        <v>7.784447739668027</v>
+        <v>10.44160030820719</v>
       </c>
       <c r="E23" t="n">
-        <v>3.691092807489324</v>
+        <v>3.345405735230089</v>
       </c>
       <c r="F23" t="n">
-        <v>3.596067404834251</v>
+        <v>7.025039111574688</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03996095592358776</v>
+        <v>0.006197753026393151</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6794510282448163</v>
+        <v>-0.9225756643891806</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7918256706633546</v>
+        <v>-0.9513902715067976</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9102892651841195</v>
+        <v>-0.9861210205514808</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.02450084656207941</v>
+        <v>-0.1614253903228811</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6015577591034742</v>
+        <v>-0.08987060199158552</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.001186405146529113</v>
+        <v>-0.007460860786185769</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>72.85330513263973</v>
+        <v>37.97233718553376</v>
       </c>
       <c r="B24" t="n">
-        <v>189.2617938010544</v>
+        <v>55.54077439542319</v>
       </c>
       <c r="C24" t="n">
-        <v>46.36821237750561</v>
+        <v>38.5876044844264</v>
       </c>
       <c r="D24" t="n">
-        <v>11.48507791687515</v>
+        <v>6.569997085347617</v>
       </c>
       <c r="E24" t="n">
-        <v>3.71619005007383</v>
+        <v>4.202465328304597</v>
       </c>
       <c r="F24" t="n">
-        <v>5.160575779313957</v>
+        <v>2.497285936865347</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01337714073608522</v>
+        <v>0.1337444096076574</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.872818439298767</v>
+        <v>-0.02149518305209231</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9194213446873328</v>
+        <v>-0.4508822532904989</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9732062619558216</v>
+        <v>-0.6092104007337963</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.07925903470235403</v>
+        <v>-0.04991116794096637</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4192192693974408</v>
+        <v>-0.5190788497641835</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.001240939629524743</v>
+        <v>-0.003774379699494068</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>82.27275789263537</v>
+        <v>75.28746407207494</v>
       </c>
       <c r="B25" t="n">
-        <v>172.7217514489725</v>
+        <v>82.40997765249008</v>
       </c>
       <c r="C25" t="n">
-        <v>46.35860079187445</v>
+        <v>38.58300194645437</v>
       </c>
       <c r="D25" t="n">
-        <v>10.09864593656197</v>
+        <v>12.46852700750853</v>
       </c>
       <c r="E25" t="n">
-        <v>2.904203443478231</v>
+        <v>2.126334971127041</v>
       </c>
       <c r="F25" t="n">
-        <v>6.012203045483046</v>
+        <v>5.521996656352256</v>
       </c>
       <c r="G25" t="n">
-        <v>0.008651738375669543</v>
+        <v>0.01171817518403916</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9107939853384698</v>
+        <v>-0.869042526267167</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9437127929131914</v>
+        <v>-0.9172032536564046</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9831870540239535</v>
+        <v>-0.9723724336526237</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.04515601214045364</v>
+        <v>-0.1154445317850717</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4895832383324874</v>
+        <v>-0.439655980540562</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0008952019795102128</v>
+        <v>-0.002700454172688133</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>37.86474707762109</v>
+        <v>43.58561590116238</v>
       </c>
       <c r="B26" t="n">
-        <v>58.32070193476157</v>
+        <v>54.47247010678867</v>
       </c>
       <c r="C26" t="n">
-        <v>46.34369785520508</v>
+        <v>38.59110901260288</v>
       </c>
       <c r="D26" t="n">
-        <v>5.791367980084758</v>
+        <v>5.765261465901215</v>
       </c>
       <c r="E26" t="n">
-        <v>2.990331126369089</v>
+        <v>4.974663257592149</v>
       </c>
       <c r="F26" t="n">
-        <v>2.410932636567726</v>
+        <v>2.938874979375776</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1376600024466129</v>
+        <v>0.07874020081170825</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1382711445639951</v>
+        <v>-0.3497314066198276</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5055408033166556</v>
+        <v>-0.6094395794489357</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6690521526107194</v>
+        <v>-0.7724616383027294</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.002650029304383667</v>
+        <v>-0.03059780227670435</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.6693875313238543</v>
+        <v>-0.6962895944131516</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.000359129524858807</v>
+        <v>-0.00459210294067175</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>76.10057751668685</v>
+        <v>77.7906941602967</v>
       </c>
       <c r="B27" t="n">
-        <v>83.49239090536325</v>
+        <v>95.88486364831876</v>
       </c>
       <c r="C27" t="n">
-        <v>46.38017545996996</v>
+        <v>38.58465594832876</v>
       </c>
       <c r="D27" t="n">
-        <v>10.45278310400567</v>
+        <v>12.45806706507903</v>
       </c>
       <c r="E27" t="n">
-        <v>2.872331457296561</v>
+        <v>4.827063442098792</v>
       </c>
       <c r="F27" t="n">
-        <v>5.49687658626864</v>
+        <v>5.791651244933427</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01132527571195802</v>
+        <v>0.01043957968672144</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8882364018205441</v>
+        <v>-0.879763206779088</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9301241372039376</v>
+        <v>-0.9245133734366938</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9774241054628053</v>
+        <v>-0.9751252307466265</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.0638749490235937</v>
+        <v>-0.08650286514273674</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.4747688281174941</v>
+        <v>-0.429258695892114</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.001671262801671131</v>
+        <v>-0.003086387943377622</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>73.34099899972264</v>
+        <v>59.19535052949391</v>
       </c>
       <c r="B28" t="n">
-        <v>189.2617938010544</v>
+        <v>71.55294033486962</v>
       </c>
       <c r="C28" t="n">
-        <v>46.36782175764893</v>
+        <v>38.58300792774075</v>
       </c>
       <c r="D28" t="n">
-        <v>11.4342824977477</v>
+        <v>8.584109659195938</v>
       </c>
       <c r="E28" t="n">
-        <v>3.659059179141956</v>
+        <v>4.581980508712427</v>
       </c>
       <c r="F28" t="n">
-        <v>5.204238776392273</v>
+        <v>4.34580900088271</v>
       </c>
       <c r="G28" t="n">
-        <v>0.01305820673131717</v>
+        <v>0.02601453608560742</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.875276253821728</v>
+        <v>-0.735683719299733</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.9212045780547135</v>
+        <v>-0.826676237352437</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9738853974316134</v>
+        <v>-0.9305161132383077</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.08059587855608712</v>
+        <v>-0.1657282190905156</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.4228623765914143</v>
+        <v>-0.6249038866867946</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.001226888670975239</v>
+        <v>-0.002701849806175521</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>46.0482122917801</v>
+        <v>47.6539465274721</v>
       </c>
       <c r="B29" t="n">
-        <v>47.70182432203721</v>
+        <v>52.3892496220397</v>
       </c>
       <c r="C29" t="n">
-        <v>46.38163314890393</v>
+        <v>38.64995751255507</v>
       </c>
       <c r="D29" t="n">
-        <v>5.006263983381625</v>
+        <v>5.040052806919933</v>
       </c>
       <c r="E29" t="n">
-        <v>2.94143436310449</v>
+        <v>4.670034428188545</v>
       </c>
       <c r="F29" t="n">
-        <v>3.136544630633707</v>
+        <v>3.288952562267061</v>
       </c>
       <c r="G29" t="n">
-        <v>0.06512339450312951</v>
+        <v>0.05609810023776193</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.518312339059115</v>
+        <v>-0.5012246403999047</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6991894062334872</v>
+        <v>-0.6896060919835394</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.8469603114347474</v>
+        <v>-0.8399222766770356</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.3936538971875761</v>
+        <v>-0.1218829279400156</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.6924441090764402</v>
+        <v>-0.6651398394230955</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.001723697224649908</v>
+        <v>-0.01832341959618303</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>89.73467626518926</v>
+        <v>68.44784620400716</v>
       </c>
       <c r="B30" t="n">
-        <v>190.5323409270514</v>
+        <v>54.16056740610847</v>
       </c>
       <c r="C30" t="n">
-        <v>46.3451108890259</v>
+        <v>38.57568077956493</v>
       </c>
       <c r="D30" t="n">
-        <v>9.148021021317435</v>
+        <v>6.285766595972697</v>
       </c>
       <c r="E30" t="n">
-        <v>3.002067686260376</v>
+        <v>4.82787955404305</v>
       </c>
       <c r="F30" t="n">
-        <v>6.793603253081481</v>
+        <v>5.179414768156944</v>
       </c>
       <c r="G30" t="n">
-        <v>0.006401690997047815</v>
+        <v>0.0152773836346658</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.9305876911297323</v>
+        <v>-0.827750818405254</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.9559396906838978</v>
+        <v>-0.8879932694820513</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.9878909532510374</v>
+        <v>-0.9605213716537102</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.06381861244013302</v>
+        <v>-0.051645499162023</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.5453242888945881</v>
+        <v>-0.683503025958712</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0004099576619996113</v>
+        <v>-0.0009921818984824637</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>57.954728282071</v>
+        <v>42.13421043362875</v>
       </c>
       <c r="B31" t="n">
-        <v>93.90006453652316</v>
+        <v>70.25757926564282</v>
       </c>
       <c r="C31" t="n">
-        <v>46.36347575355199</v>
+        <v>38.60172262168807</v>
       </c>
       <c r="D31" t="n">
-        <v>7.578565860513009</v>
+        <v>6.14260254222434</v>
       </c>
       <c r="E31" t="n">
-        <v>2.019309404148991</v>
+        <v>4.663006798762399</v>
       </c>
       <c r="F31" t="n">
-        <v>4.090035394114605</v>
+        <v>2.838378622351545</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0285828426596438</v>
+        <v>0.08968845696265977</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7544913485006693</v>
+        <v>-0.2806988980137551</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8389011764857616</v>
+        <v>-0.5745284886910994</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.9369191967735779</v>
+        <v>-0.7398446751724392</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.1681108155960924</v>
+        <v>-0.05280092763316991</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.6348229879527262</v>
+        <v>-0.6876718744496707</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.001070558872637148</v>
+        <v>-0.007068611727215901</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>45.74517624691715</v>
+        <v>92.50401400122959</v>
       </c>
       <c r="B32" t="n">
-        <v>68.67734182402152</v>
+        <v>80.24451782068107</v>
       </c>
       <c r="C32" t="n">
-        <v>46.36754379521771</v>
+        <v>38.59774133233793</v>
       </c>
       <c r="D32" t="n">
-        <v>5.000037833920469</v>
+        <v>10.27472615162984</v>
       </c>
       <c r="E32" t="n">
-        <v>2.971936534915449</v>
+        <v>3.853822959863729</v>
       </c>
       <c r="F32" t="n">
-        <v>3.055272482983264</v>
+        <v>7.297812499625087</v>
       </c>
       <c r="G32" t="n">
-        <v>0.06684618823954054</v>
+        <v>0.005697995214131639</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5087006589791288</v>
+        <v>-0.9273398944653201</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6938771725345091</v>
+        <v>-0.9538256205033051</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8428805453780061</v>
+        <v>-0.9871536814426044</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.2027773113425998</v>
+        <v>-0.06535701264264641</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.7166676368920476</v>
+        <v>-0.5340910997587609</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.001216890104511017</v>
+        <v>-0.006139644212183326</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>60.29811635091578</v>
+        <v>93.43460391350061</v>
       </c>
       <c r="B33" t="n">
-        <v>54.46777320249407</v>
+        <v>53.60991236435509</v>
       </c>
       <c r="C33" t="n">
-        <v>46.38144183772803</v>
+        <v>40.02433302250599</v>
       </c>
       <c r="D33" t="n">
-        <v>5.006369573044331</v>
+        <v>9.734051546400273</v>
       </c>
       <c r="E33" t="n">
-        <v>2.94143436310449</v>
+        <v>4.761833498221103</v>
       </c>
       <c r="F33" t="n">
-        <v>4.327843196603442</v>
+        <v>7.398127788999924</v>
       </c>
       <c r="G33" t="n">
-        <v>0.02428530059131012</v>
+        <v>0.005506691346721647</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7821759359910945</v>
+        <v>-0.9299568681039629</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8572732208686989</v>
+        <v>-0.9559664812120557</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.9462529615476259</v>
+        <v>-0.9878206479868323</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.07531858640359937</v>
+        <v>-0.09636054081962973</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.5230283429239198</v>
+        <v>-0.05498339031886346</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.001716815584209272</v>
+        <v>-0.3390110385847318</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>42.80486304310437</v>
+        <v>49.23593962476572</v>
       </c>
       <c r="B34" t="n">
-        <v>55.31988507017735</v>
+        <v>52.3892496220397</v>
       </c>
       <c r="C34" t="n">
-        <v>46.36003343303624</v>
+        <v>38.58607788925232</v>
       </c>
       <c r="D34" t="n">
-        <v>5.016394855639441</v>
+        <v>5.040052806919933</v>
       </c>
       <c r="E34" t="n">
-        <v>3.006179475372477</v>
+        <v>4.772102575908636</v>
       </c>
       <c r="F34" t="n">
-        <v>2.770001102506212</v>
+        <v>3.468516120809995</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0858992795014973</v>
+        <v>0.04965113662193516</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4017601673550811</v>
+        <v>-0.5472155807813062</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6366334356025137</v>
+        <v>-0.7150811862447567</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7960817029886801</v>
+        <v>-0.8591561065210337</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.03800898137050458</v>
+        <v>-0.2715662975755224</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.7039627597604472</v>
+        <v>-0.5959276414164999</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.0009467354108912131</v>
+        <v>-0.003418174158874854</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>51.4783834598787</v>
+        <v>67.26905719820667</v>
       </c>
       <c r="B35" t="n">
-        <v>100.6254567671969</v>
+        <v>95.62894993535645</v>
       </c>
       <c r="C35" t="n">
-        <v>46.36650836168956</v>
+        <v>38.58460158778349</v>
       </c>
       <c r="D35" t="n">
-        <v>8.565733860130017</v>
+        <v>13.09969165429611</v>
       </c>
       <c r="E35" t="n">
-        <v>2.570683932627043</v>
+        <v>4.924750915916762</v>
       </c>
       <c r="F35" t="n">
-        <v>3.550496069257966</v>
+        <v>4.790779232131184</v>
       </c>
       <c r="G35" t="n">
-        <v>0.04457084070870176</v>
+        <v>0.01762887734329295</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6514543422784904</v>
+        <v>-0.8178667300410545</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7748637020851324</v>
+        <v>-0.8807864230719806</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8997338420579136</v>
+        <v>-0.9573568940282235</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.1488559619993094</v>
+        <v>-0.0243941308059001</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.5918196569154688</v>
+        <v>-0.3669049807618863</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.001179644600125915</v>
+        <v>-0.003073703816147549</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>39.19933743676443</v>
+        <v>82.72803428193609</v>
       </c>
       <c r="B36" t="n">
-        <v>56.40067170864609</v>
+        <v>74.51339728466785</v>
       </c>
       <c r="C36" t="n">
-        <v>46.35484804542605</v>
+        <v>39.24066764705982</v>
       </c>
       <c r="D36" t="n">
-        <v>5.591014159131191</v>
+        <v>11.36874602202548</v>
       </c>
       <c r="E36" t="n">
-        <v>4.590316202480941</v>
+        <v>4.787628652201595</v>
       </c>
       <c r="F36" t="n">
-        <v>2.507074544889735</v>
+        <v>6.242956520685475</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1204135577350347</v>
+        <v>0.008381210291380692</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2227585406557281</v>
+        <v>-0.9004711740322213</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5462571082018457</v>
+        <v>-0.9381431136464266</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.7114240295544701</v>
+        <v>-0.9807255386059632</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.02057689301552423</v>
+        <v>-0.07983992982260105</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.6757249551201822</v>
+        <v>-0.4799487506866577</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.0007602122090432354</v>
+        <v>-0.1561557843139581</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>57.27576541226901</v>
+        <v>48.31919989888772</v>
       </c>
       <c r="B37" t="n">
-        <v>78.54252911079739</v>
+        <v>52.3892496220397</v>
       </c>
       <c r="C37" t="n">
-        <v>46.43107509353845</v>
+        <v>38.65003985808447</v>
       </c>
       <c r="D37" t="n">
-        <v>7.582065200452424</v>
+        <v>5.034545604527667</v>
       </c>
       <c r="E37" t="n">
-        <v>3.00578806869876</v>
+        <v>4.670034428188545</v>
       </c>
       <c r="F37" t="n">
-        <v>4.018659710792468</v>
+        <v>3.363500718506392</v>
       </c>
       <c r="G37" t="n">
-        <v>0.02984874628121476</v>
+        <v>0.05326117010137976</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7458228340364051</v>
+        <v>-0.5212981035133198</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8333155882589469</v>
+        <v>-0.7006506238455017</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.933964719684689</v>
+        <v>-0.8483923463917789</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.1434031184381205</v>
+        <v>-0.18355170069073</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.6303146324136496</v>
+        <v>-0.6360350044236623</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.003502169831154952</v>
+        <v>-0.01834263355304261</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>79.56640240201189</v>
+        <v>41.44121482507525</v>
       </c>
       <c r="B38" t="n">
-        <v>175.2068160212272</v>
+        <v>53.15864851409113</v>
       </c>
       <c r="C38" t="n">
-        <v>46.3560235349492</v>
+        <v>38.59857345494656</v>
       </c>
       <c r="D38" t="n">
-        <v>10.45084488162267</v>
+        <v>6.303395342604844</v>
       </c>
       <c r="E38" t="n">
-        <v>3.996773569634613</v>
+        <v>4.978744240672743</v>
       </c>
       <c r="F38" t="n">
-        <v>5.748841210611376</v>
+        <v>2.789635430008719</v>
       </c>
       <c r="G38" t="n">
-        <v>0.009736908048433166</v>
+        <v>0.09560128070695689</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9016900034819696</v>
+        <v>-0.2442592835856035</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9382735894406461</v>
+        <v>-0.5564562035669035</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9809019132828664</v>
+        <v>-0.7221998185649849</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.04504139616725037</v>
+        <v>-0.05805020489128805</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.4693665741035229</v>
+        <v>-0.6835572130238843</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.0008024956574716201</v>
+        <v>-0.006333806154198013</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>98.79349175974802</v>
+        <v>43.31318318785081</v>
       </c>
       <c r="B39" t="n">
-        <v>87.5845437176754</v>
+        <v>54.457356084577</v>
       </c>
       <c r="C39" t="n">
-        <v>46.36017693493391</v>
+        <v>38.59085116574941</v>
       </c>
       <c r="D39" t="n">
-        <v>7.69645498140991</v>
+        <v>5.897526340815988</v>
       </c>
       <c r="E39" t="n">
-        <v>3.059875391141654</v>
+        <v>4.914245629523567</v>
       </c>
       <c r="F39" t="n">
-        <v>7.810809140308766</v>
+        <v>2.927058207883895</v>
       </c>
       <c r="G39" t="n">
-        <v>0.004625594807005793</v>
+        <v>0.08067895990281404</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9473073798791699</v>
+        <v>-0.3374458791244</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9667815212919338</v>
+        <v>-0.6031534589062887</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9915450094749955</v>
+        <v>-0.766729297655886</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.0678976251073652</v>
+        <v>-0.05452553522344634</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.6129942723096062</v>
+        <v>-0.6946720251778642</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.0009518973072508938</v>
+        <v>-0.004531938674862401</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>47.50222721545104</v>
+        <v>80.87585491872528</v>
       </c>
       <c r="B40" t="n">
-        <v>67.24516933771264</v>
+        <v>95.68200864012567</v>
       </c>
       <c r="C40" t="n">
-        <v>46.36022797876919</v>
+        <v>38.58993756086766</v>
       </c>
       <c r="D40" t="n">
-        <v>5.000305666062514</v>
+        <v>11.69273168621304</v>
       </c>
       <c r="E40" t="n">
-        <v>2.542119844008299</v>
+        <v>4.200145287523707</v>
       </c>
       <c r="F40" t="n">
-        <v>3.172031559227185</v>
+        <v>6.044841150176028</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0581352906702693</v>
+        <v>0.009072196808560855</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5604419415042095</v>
+        <v>-0.892724285193336</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7226373087917576</v>
+        <v>-0.9329220056520315</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8643577863050088</v>
+        <v>-0.9785961934984072</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.04754726645873771</v>
+        <v>-0.02935979632416565</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.7016717560199955</v>
+        <v>-0.4512404662959175</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.0009537334013494093</v>
+        <v>-0.004318764202453224</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>89.09859803699845</v>
+        <v>77.20085823697558</v>
       </c>
       <c r="B41" t="n">
-        <v>190.5323409270514</v>
+        <v>97.02255199808576</v>
       </c>
       <c r="C41" t="n">
-        <v>46.3451108890259</v>
+        <v>38.58465594832876</v>
       </c>
       <c r="D41" t="n">
-        <v>9.235696351753468</v>
+        <v>12.13907099989165</v>
       </c>
       <c r="E41" t="n">
-        <v>2.287248134518362</v>
+        <v>4.903836206147728</v>
       </c>
       <c r="F41" t="n">
-        <v>6.724746479438325</v>
+        <v>5.688259234612129</v>
       </c>
       <c r="G41" t="n">
-        <v>0.006559843768318209</v>
+        <v>0.01070272345634154</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.9291510519551772</v>
+        <v>-0.8771167666481906</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9550315561495342</v>
+        <v>-0.9225646792606279</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9875625733806003</v>
+        <v>-0.9744113084022791</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.06246969126627419</v>
+        <v>-0.02625468384692112</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.5405727401763059</v>
+        <v>-0.425056114938451</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.0004099576619996113</v>
+        <v>-0.003086387943377622</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>38.58400871860092</v>
+        <v>41.76864280107925</v>
       </c>
       <c r="B42" t="n">
-        <v>56.40067170864609</v>
+        <v>68.08409222409482</v>
       </c>
       <c r="C42" t="n">
-        <v>46.35484804542605</v>
+        <v>38.66753326050462</v>
       </c>
       <c r="D42" t="n">
-        <v>5.591014159131191</v>
+        <v>6.143091650900868</v>
       </c>
       <c r="E42" t="n">
-        <v>4.590316202480941</v>
+        <v>4.76829715526466</v>
       </c>
       <c r="F42" t="n">
-        <v>2.461449285411</v>
+        <v>2.803576784264998</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1278826785259758</v>
+        <v>0.09271664621805377</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1853665450495885</v>
+        <v>-0.2618173646412688</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5281179990118683</v>
+        <v>-0.5651423328294444</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.6928861909837749</v>
+        <v>-0.7307495992315254</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.01780081643705849</v>
+        <v>-0.03108687041788258</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.6680037786406212</v>
+        <v>-0.685501316631408</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.0007602122090432354</v>
+        <v>-0.02242442745107903</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>38.12669660857818</v>
+        <v>38.96370157268588</v>
       </c>
       <c r="B43" t="n">
-        <v>67.23966946779173</v>
+        <v>54.48862513055567</v>
       </c>
       <c r="C43" t="n">
-        <v>46.37370028859445</v>
+        <v>38.60449938474996</v>
       </c>
       <c r="D43" t="n">
-        <v>5.846722191376298</v>
+        <v>6.322586396220081</v>
       </c>
       <c r="E43" t="n">
-        <v>2.310301372932262</v>
+        <v>3.424283782882138</v>
       </c>
       <c r="F43" t="n">
-        <v>2.431275767594464</v>
+        <v>2.557404832325718</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1341634976115016</v>
+        <v>0.1210086347224167</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.1556718026392548</v>
+        <v>-0.09388577268725964</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5138173508371376</v>
+        <v>-0.4845079149691695</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.6778572473697861</v>
+        <v>-0.6471440382251539</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.001866278117796593</v>
+        <v>-0.03798759950091574</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.6748409018652997</v>
+        <v>-0.4804156386652507</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.001438344881494088</v>
+        <v>-0.007716523108323853</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43.25719024883809</v>
+        <v>38.96370157268588</v>
       </c>
       <c r="B44" t="n">
-        <v>55.21716688646282</v>
+        <v>54.48862513055567</v>
       </c>
       <c r="C44" t="n">
-        <v>46.36003343303624</v>
+        <v>38.60449938474996</v>
       </c>
       <c r="D44" t="n">
-        <v>5.019528314578213</v>
+        <v>6.322586396220081</v>
       </c>
       <c r="E44" t="n">
-        <v>3.009828360384539</v>
+        <v>3.430528610662009</v>
       </c>
       <c r="F44" t="n">
-        <v>2.81591757796834</v>
+        <v>2.557404832325718</v>
       </c>
       <c r="G44" t="n">
-        <v>0.08254306645868185</v>
+        <v>0.1210086347224167</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.4201317465778372</v>
+        <v>-0.09388577268725964</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.646271854103567</v>
+        <v>-0.4845079149691695</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.8043346727081421</v>
+        <v>-0.6471440382251539</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.07723491831949653</v>
+        <v>-0.03798759950091574</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.7067785229000972</v>
+        <v>-0.4804156386652507</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0009467354108912131</v>
+        <v>-0.007716523108323853</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44.46935815658169</v>
+        <v>62.12961463184327</v>
       </c>
       <c r="B45" t="n">
-        <v>67.3018570108087</v>
+        <v>61.57112155053389</v>
       </c>
       <c r="C45" t="n">
-        <v>46.3635846998155</v>
+        <v>38.65003985808447</v>
       </c>
       <c r="D45" t="n">
-        <v>5.006369573044331</v>
+        <v>8.562640403630965</v>
       </c>
       <c r="E45" t="n">
-        <v>2.029731185449138</v>
+        <v>4.611292806298369</v>
       </c>
       <c r="F45" t="n">
-        <v>2.938678800300824</v>
+        <v>4.6805293244655</v>
       </c>
       <c r="G45" t="n">
-        <v>0.07434057991020149</v>
+        <v>0.02181271671090158</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4657744255464991</v>
+        <v>-0.7707672293564249</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6705626016764935</v>
+        <v>-0.8493639659240266</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.8244661189644815</v>
+        <v>-0.9424141705591906</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.174886094921783</v>
+        <v>-0.2665465742600919</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.7143243385627976</v>
+        <v>-0.6434875593350073</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.001074477770784539</v>
+        <v>-0.01834263355304261</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>86.67005236222775</v>
+        <v>95.68174965651095</v>
       </c>
       <c r="B46" t="n">
-        <v>74.12989675244401</v>
+        <v>53.67567746928414</v>
       </c>
       <c r="C46" t="n">
-        <v>46.34644927964951</v>
+        <v>38.60022676239963</v>
       </c>
       <c r="D46" t="n">
-        <v>9.467933350530283</v>
+        <v>9.716702876009663</v>
       </c>
       <c r="E46" t="n">
-        <v>2.296653450666638</v>
+        <v>4.914026421446195</v>
       </c>
       <c r="F46" t="n">
-        <v>6.454294137676197</v>
+        <v>7.652747043710656</v>
       </c>
       <c r="G46" t="n">
-        <v>0.007212259176349761</v>
+        <v>0.005081586594754483</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.9232800664961143</v>
+        <v>-0.9340813900293331</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9513618486481694</v>
+        <v>-0.9581110381726762</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.9861995869398813</v>
+        <v>-0.9886886453713493</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.03877591834215657</v>
+        <v>-0.05336824632313483</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.5224313346434236</v>
+        <v>-0.5567324663026404</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.0004581008141047828</v>
+        <v>-0.006719577893247453</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>60.33931923033763</v>
+        <v>42.75732168105742</v>
       </c>
       <c r="B47" t="n">
-        <v>54.45278312059279</v>
+        <v>53.16125966046822</v>
       </c>
       <c r="C47" t="n">
-        <v>46.38144183772803</v>
+        <v>38.58051604597338</v>
       </c>
       <c r="D47" t="n">
-        <v>5.002260553494818</v>
+        <v>5.855739958618377</v>
       </c>
       <c r="E47" t="n">
-        <v>2.94143436310449</v>
+        <v>4.767627784864631</v>
       </c>
       <c r="F47" t="n">
-        <v>4.332389554300149</v>
+        <v>2.865423931634314</v>
       </c>
       <c r="G47" t="n">
-        <v>0.02422491089553946</v>
+        <v>0.0847150949837204</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.7826128016580077</v>
+        <v>-0.311548485203798</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8575629822514438</v>
+        <v>-0.590029272630112</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.9463949534018875</v>
+        <v>-0.7545735830691865</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.07705786062521308</v>
+        <v>-0.001387384958654618</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.5225885322988232</v>
+        <v>-0.6913715974812784</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.001716815584209272</v>
+        <v>-0.002120410727119854</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>82.25626338054427</v>
+        <v>48.64207431355604</v>
       </c>
       <c r="B48" t="n">
-        <v>175.2997488989468</v>
+        <v>42.81812269884692</v>
       </c>
       <c r="C48" t="n">
-        <v>46.36055336717158</v>
+        <v>38.62561331453534</v>
       </c>
       <c r="D48" t="n">
-        <v>10.09864593656197</v>
+        <v>5.469456511996373</v>
       </c>
       <c r="E48" t="n">
-        <v>2.904203443478231</v>
+        <v>4.670034428188545</v>
       </c>
       <c r="F48" t="n">
-        <v>6.010352017284935</v>
+        <v>3.452911132128435</v>
       </c>
       <c r="G48" t="n">
-        <v>0.008657755900208303</v>
+        <v>0.05203488291470859</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.910742252322822</v>
+        <v>-0.5313154166136985</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9436817168600561</v>
+        <v>-0.70636232793753</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9831742976973814</v>
+        <v>-0.8527442524245231</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.04478338961797401</v>
+        <v>-0.5412787154492535</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.4894600231770055</v>
+        <v>-0.1029591017713144</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0009654379239849214</v>
+        <v>-0.01264310672491137</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>50.40103569412435</v>
+        <v>55.79589595873878</v>
       </c>
       <c r="B49" t="n">
-        <v>64.54475946365332</v>
+        <v>71.55294033486962</v>
       </c>
       <c r="C49" t="n">
-        <v>46.35918162324759</v>
+        <v>38.58300792774075</v>
       </c>
       <c r="D49" t="n">
-        <v>5.412291212474864</v>
+        <v>8.647250889509946</v>
       </c>
       <c r="E49" t="n">
-        <v>2.95979508519803</v>
+        <v>4.581980508712427</v>
       </c>
       <c r="F49" t="n">
-        <v>3.441182816581921</v>
+        <v>3.985061306961804</v>
       </c>
       <c r="G49" t="n">
-        <v>0.04679232880455524</v>
+        <v>0.03233857822959806</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.6308176692574902</v>
+        <v>-0.6852920949964486</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.7631093581793057</v>
+        <v>-0.7952146124331242</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.89224186794158</v>
+        <v>-0.9125094168183653</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.07561409513399193</v>
+        <v>-0.05999067385706707</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.6500892669471064</v>
+        <v>-0.6033740077386789</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0009160950227299949</v>
+        <v>-0.002701849806175521</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>44.46935815658169</v>
+        <v>62.46870718342713</v>
       </c>
       <c r="B50" t="n">
-        <v>67.30171923417211</v>
+        <v>54.64764686961836</v>
       </c>
       <c r="C50" t="n">
-        <v>46.3635846998155</v>
+        <v>33.61733733964464</v>
       </c>
       <c r="D50" t="n">
-        <v>5.006369573044331</v>
+        <v>8.584109659195938</v>
       </c>
       <c r="E50" t="n">
-        <v>2.027555172847438</v>
+        <v>4.966712409993107</v>
       </c>
       <c r="F50" t="n">
-        <v>2.938678800300824</v>
+        <v>4.716737892363555</v>
       </c>
       <c r="G50" t="n">
-        <v>0.07434057991020149</v>
+        <v>0.021384076212584</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.4657744255464991</v>
+        <v>-0.7744118888885184</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6705626016764935</v>
+        <v>-0.8517641518165709</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.8244661189644815</v>
+        <v>-0.9436189219509397</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.174886094921783</v>
+        <v>-0.1750232441234211</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.7143243385627976</v>
+        <v>-0.6456351454950384</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.001074477770784539</v>
+        <v>-0.1125342490616327</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>77.77198747698702</v>
+        <v>59.19535052949391</v>
       </c>
       <c r="B51" t="n">
-        <v>175.2068160212272</v>
+        <v>71.71567084666141</v>
       </c>
       <c r="C51" t="n">
-        <v>46.35589810095307</v>
+        <v>38.58300792774075</v>
       </c>
       <c r="D51" t="n">
-        <v>11.64346865807799</v>
+        <v>8.584109659195938</v>
       </c>
       <c r="E51" t="n">
-        <v>2.938500046618712</v>
+        <v>4.581440279575614</v>
       </c>
       <c r="F51" t="n">
-        <v>5.699850808479726</v>
+        <v>4.34580900088271</v>
       </c>
       <c r="G51" t="n">
-        <v>0.01062319150310828</v>
+        <v>0.02601453608560742</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.8948145555095052</v>
+        <v>-0.735683719299733</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9340690735668821</v>
+        <v>-0.826676237352437</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.9791122488605517</v>
+        <v>-0.9305161132383077</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.1965038586555052</v>
+        <v>-0.1657282190905156</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.4559621694891416</v>
+        <v>-0.6249038866867946</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0007979836802899423</v>
+        <v>-0.002701849806175521</v>
       </c>
     </row>
   </sheetData>
